--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProdPersonIssue.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProdPersonIssue.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19815" windowHeight="8820"/>
+    <workbookView windowWidth="21600" windowHeight="9765"/>
   </bookViews>
   <sheets>
     <sheet name="发行登记要素" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
-    <sheet name="版本号 1.1.0" sheetId="4" r:id="rId3"/>
+    <sheet name="版本号 1.1.9" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36">
   <si>
     <t>产品登记编码</t>
   </si>
@@ -39,19 +39,22 @@
     <t>产品终止日期</t>
   </si>
   <si>
-    <t>管理方式</t>
-  </si>
-  <si>
     <t>是否为结构化（分级）产品</t>
   </si>
   <si>
-    <t>业绩比较基准上限%</t>
-  </si>
-  <si>
-    <t>业绩比较基准下限%</t>
-  </si>
-  <si>
-    <t>业绩比较基准说明</t>
+    <t>层级类别</t>
+  </si>
+  <si>
+    <t>预计客户最低年收益率 %</t>
+  </si>
+  <si>
+    <t>预计客户最高年收益率 %</t>
+  </si>
+  <si>
+    <t>平均预计客户年收益率%</t>
+  </si>
+  <si>
+    <t>收益率分档情况说明</t>
   </si>
   <si>
     <t>开放模式</t>
@@ -81,16 +84,16 @@
     <t>开放期业务说明</t>
   </si>
   <si>
-    <t>资金托管账号</t>
-  </si>
-  <si>
-    <t>资金托管账户</t>
-  </si>
-  <si>
-    <t>公私募理财产品发行登记数据批量模板填写说明</t>
+    <t>个人理财产品发行登记数据批量模板填写说明</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>1.为使导入成功，所有单元格都必须保持模板原有的格式，如须粘贴数据请使用</t>
     </r>
     <r>
@@ -128,7 +131,25 @@
     <t>版本号</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1.1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>9</t>
+    </r>
   </si>
   <si>
     <t>发布时间</t>
@@ -137,9 +158,59 @@
     <t>版本说明</t>
   </si>
   <si>
+    <t xml:space="preserve">
+1.“预计客户最低年收益率”允许为负
+2.“平均预计客户年收益率”允许为负
+</t>
+  </si>
+  <si>
     <r>
-      <t>1.删除要素：“层级类别”、“预计客户最低年收益率 %”、“预计客户最高年收益率 %”、“平均预计客户年收益率%”、“收益率分档情况说明”；
-2.新增要素：“业绩比较基准上限%</t>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1.1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>8</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">
+1.增加“收益率分档情况说明”要素
+2.增加“是否为结构化（分级）产品”、“层级类别”要素
+3.增加“开放模式”、“规律开放周期”、“其他规律开放周期 (天)”、“无规律开放说明”、“首次开放周期起始日”、“节假日是否开放”、“平均开放次数（年化）”、“开放期业务”、“开放期业务说明”要素
+4.产品定位要素变更为产品登记编码
+</t>
+  </si>
+  <si>
+    <t>1.1.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+1.增加"平均预计客户年收益率%"、"预计客户最低年收益率 %"、"预计客户最高年收益率 %"要素
+2.“产品预计终止日期”更名为“产品终止日期”
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1.1.</t>
     </r>
     <r>
       <rPr>
@@ -148,62 +219,13 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>”、“业绩比较基准下限</t>
+      <t>6</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">”、“业绩比较基准说明”；
+  </si>
+  <si>
+    <t xml:space="preserve">
+1.去掉“实际募集金额”要素
 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0</t>
-    </r>
-  </si>
-  <si>
-    <t>新增公/私募理财产品发行导入模板</t>
   </si>
 </sst>
 </file>
@@ -212,15 +234,15 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="8">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00000_ "/>
     <numFmt numFmtId="177" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="0_ "/>
+    <numFmt numFmtId="178" formatCode="0_ "/>
+    <numFmt numFmtId="179" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,57 +277,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="52"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color indexed="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -320,23 +300,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color indexed="56"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -351,7 +329,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color indexed="56"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -359,26 +337,37 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color indexed="56"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color indexed="9"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="60"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color indexed="56"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
@@ -394,21 +383,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
@@ -416,11 +390,20 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color indexed="63"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -428,71 +411,7 @@
       <color indexed="56"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="20"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color indexed="23"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="52"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="62"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -501,7 +420,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -516,12 +435,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor indexed="44"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -534,19 +447,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="22"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="11"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="31"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="52"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="36"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="46"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="46"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="62"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="51"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -558,198 +597,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="11"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="31"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="42"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="26"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="49"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="43"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="30"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="36"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="52"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="53"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="51"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="29"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="62"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="45"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="27"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="47"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="55"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="10"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="57"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="18">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -773,15 +626,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -802,21 +651,6 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="23"/>
-      </left>
-      <right style="thin">
-        <color indexed="23"/>
-      </right>
-      <top style="thin">
-        <color indexed="23"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="23"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -831,21 +665,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="22"/>
-      </left>
-      <right style="thin">
-        <color indexed="22"/>
-      </right>
-      <top style="thin">
-        <color indexed="22"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -853,24 +672,6 @@
       </top>
       <bottom style="double">
         <color indexed="62"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="62"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="30"/>
       </bottom>
       <diagonal/>
     </border>
@@ -917,23 +718,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="63"/>
-      </left>
-      <right style="thin">
-        <color indexed="63"/>
-      </right>
-      <top style="thin">
-        <color indexed="63"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="63"/>
+      <bottom style="medium">
+        <color indexed="30"/>
       </bottom>
       <diagonal/>
     </border>
@@ -942,49 +728,22 @@
       <right/>
       <top/>
       <bottom style="thick">
-        <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="63"/>
-      </left>
-      <right style="double">
-        <color indexed="63"/>
-      </right>
-      <top style="double">
-        <color indexed="63"/>
-      </top>
-      <bottom style="double">
-        <color indexed="63"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color indexed="52"/>
+        <color indexed="62"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="93">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -996,292 +755,175 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellStyleXfs>
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="39" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="38" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="27">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="78" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="3" borderId="0" xfId="78" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="61" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="61" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="61" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="77" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="77" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="77" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="77" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -1303,151 +945,92 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="93">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 1 2" xfId="2"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="3" builtinId="38"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="货币" xfId="5" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="6" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="7" builtinId="39"/>
-    <cellStyle name="计算 2" xfId="8"/>
-    <cellStyle name="差" xfId="9" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="10" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="11" builtinId="40"/>
-    <cellStyle name="超链接" xfId="12" builtinId="8"/>
-    <cellStyle name="百分比" xfId="13" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="14" builtinId="9"/>
-    <cellStyle name="注释" xfId="15" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="16" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="17" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="18" builtinId="11"/>
-    <cellStyle name="标题" xfId="19" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="20" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="21" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="22" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="23" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="24" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="25" builtinId="44"/>
-    <cellStyle name="输出" xfId="26" builtinId="21"/>
-    <cellStyle name="计算" xfId="27" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="28" builtinId="23"/>
-    <cellStyle name="40% - 强调文字颜色 4 2" xfId="29"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="30" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="31" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="32" builtinId="24"/>
-    <cellStyle name="40% - 强调文字颜色 1 2" xfId="33"/>
-    <cellStyle name="汇总" xfId="34" builtinId="25"/>
-    <cellStyle name="好" xfId="35" builtinId="26"/>
-    <cellStyle name="40% - 强调文字颜色 2 2" xfId="36"/>
-    <cellStyle name="适中" xfId="37" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="38" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="39" builtinId="29"/>
-    <cellStyle name="40% - 强调文字颜色 5 2" xfId="40"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="41" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="42" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 4 2" xfId="43"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="44" builtinId="34"/>
-    <cellStyle name="输出 2" xfId="45"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="46" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="47" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="48" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="49" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="50" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="51" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="52" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="53" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="54" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="55" builtinId="51"/>
-    <cellStyle name="适中 2" xfId="56"/>
-    <cellStyle name="40% - 强调文字颜色 6 2" xfId="57"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="58" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 2 2" xfId="59"/>
-    <cellStyle name="20% - 强调文字颜色 3 2" xfId="60"/>
-    <cellStyle name="常规 3" xfId="61"/>
-    <cellStyle name="20% - 强调文字颜色 4 2" xfId="62"/>
-    <cellStyle name="20% - 强调文字颜色 5 2" xfId="63"/>
-    <cellStyle name="20% - 强调文字颜色 6 2" xfId="64"/>
-    <cellStyle name="40% - 强调文字颜色 3 2" xfId="65"/>
-    <cellStyle name="60% - 强调文字颜色 1 2" xfId="66"/>
-    <cellStyle name="60% - 强调文字颜色 2 2" xfId="67"/>
-    <cellStyle name="60% - 强调文字颜色 3 2" xfId="68"/>
-    <cellStyle name="60% - 强调文字颜色 5 2" xfId="69"/>
-    <cellStyle name="60% - 强调文字颜色 6 2" xfId="70"/>
-    <cellStyle name="标题 1 2" xfId="71"/>
-    <cellStyle name="标题 2 2" xfId="72"/>
-    <cellStyle name="标题 3 2" xfId="73"/>
-    <cellStyle name="标题 4 2" xfId="74"/>
-    <cellStyle name="标题 5" xfId="75"/>
-    <cellStyle name="差 2" xfId="76"/>
-    <cellStyle name="常规 2" xfId="77"/>
-    <cellStyle name="常规 2 2" xfId="78"/>
-    <cellStyle name="好 2" xfId="79"/>
-    <cellStyle name="汇总 2" xfId="80"/>
-    <cellStyle name="检查单元格 2" xfId="81"/>
-    <cellStyle name="解释性文本 2" xfId="82"/>
-    <cellStyle name="警告文本 2" xfId="83"/>
-    <cellStyle name="链接单元格 2" xfId="84"/>
-    <cellStyle name="强调文字颜色 1 2" xfId="85"/>
-    <cellStyle name="强调文字颜色 2 2" xfId="86"/>
-    <cellStyle name="强调文字颜色 3 2" xfId="87"/>
-    <cellStyle name="强调文字颜色 4 2" xfId="88"/>
-    <cellStyle name="强调文字颜色 5 2" xfId="89"/>
-    <cellStyle name="强调文字颜色 6 2" xfId="90"/>
-    <cellStyle name="输入 2" xfId="91"/>
-    <cellStyle name="注释 2" xfId="92"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
       <color rgb="00FF0000"/>
       <color rgb="0099CC00"/>
-      <color rgb="0092D050"/>
       <color rgb="0099CCFF"/>
       <color rgb="00000000"/>
     </mruColors>
@@ -1512,7 +1095,7 @@
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -1547,7 +1130,7 @@
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -1747,57 +1330,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W168"/>
+  <dimension ref="A1:V169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="27.25" style="11" customWidth="1"/>
-    <col min="2" max="2" width="16.125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="14.125" style="11" customWidth="1"/>
-    <col min="4" max="6" width="14.125" style="11"/>
-    <col min="7" max="8" width="18.625" style="11"/>
-    <col min="9" max="9" width="27.5" style="11"/>
-    <col min="10" max="11" width="22.375" style="12" customWidth="1"/>
-    <col min="12" max="12" width="49.25" style="13" customWidth="1"/>
-    <col min="13" max="13" width="14.25" style="14"/>
-    <col min="14" max="14" width="14.125" style="14"/>
-    <col min="15" max="15" width="24.5" style="15"/>
-    <col min="16" max="16" width="25.125" style="14" customWidth="1"/>
-    <col min="17" max="17" width="20.75" style="14"/>
-    <col min="18" max="18" width="16.375" style="14"/>
-    <col min="19" max="19" width="23" style="16"/>
-    <col min="20" max="20" width="11.875" style="14"/>
-    <col min="21" max="21" width="16.375" style="17"/>
-    <col min="22" max="22" width="14.5" style="18" customWidth="1"/>
-    <col min="23" max="23" width="13.5" style="18" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="19"/>
+    <col min="1" max="1" width="15.25" style="14" customWidth="1"/>
+    <col min="2" max="2" width="16.125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="14.125" style="14" customWidth="1"/>
+    <col min="4" max="6" width="14.125" style="14"/>
+    <col min="7" max="7" width="18.625" style="14"/>
+    <col min="8" max="8" width="27.5" style="14"/>
+    <col min="9" max="9" width="14.25" style="14"/>
+    <col min="10" max="10" width="24.25" style="15" customWidth="1"/>
+    <col min="11" max="11" width="24" style="15" customWidth="1"/>
+    <col min="12" max="12" width="22.375" style="15" customWidth="1"/>
+    <col min="13" max="13" width="30.5" style="16" customWidth="1"/>
+    <col min="14" max="14" width="14.25" style="17"/>
+    <col min="15" max="15" width="14.125" style="17"/>
+    <col min="16" max="16" width="24.5" style="18"/>
+    <col min="17" max="17" width="25.125" style="17" customWidth="1"/>
+    <col min="18" max="18" width="20.75" style="17"/>
+    <col min="19" max="19" width="16.375" style="17"/>
+    <col min="20" max="20" width="23" style="19"/>
+    <col min="21" max="21" width="11.875" style="17"/>
+    <col min="22" max="22" width="16.375" style="17"/>
+    <col min="23" max="16384" width="9" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="1" ht="24.75" customHeight="1" spans="1:23">
-      <c r="A1" s="20" t="s">
+    <row r="1" s="13" customFormat="1" ht="24.75" customHeight="1" spans="1:22">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="21" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="23" t="s">
@@ -1809,49 +1393,39 @@
       <c r="L1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="M1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="N1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="24" t="s">
+      <c r="O1" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="P1" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="Q1" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="20" t="s">
+      <c r="R1" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="25" t="s">
+      <c r="S1" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="20" t="s">
+      <c r="T1" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="26" t="s">
+      <c r="U1" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="20" t="s">
+      <c r="V1" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="L2" s="14"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
+    </row>
+    <row r="2" spans="13:13">
+      <c r="M2" s="17"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="22"/>
@@ -2668,47 +2242,59 @@
       <c r="B168" s="22"/>
       <c r="C168" s="22"/>
     </row>
+    <row r="169" spans="1:3">
+      <c r="A169" s="22"/>
+      <c r="B169" s="22"/>
+      <c r="C169" s="22"/>
+    </row>
   </sheetData>
-  <sheetProtection formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H65536">
-      <formula1>"01 集合管理,02 单独管理"</formula1>
+  <sheetProtection password="EC2B" sheet="1" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <dataValidations count="12">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值整数位不可超过3位，小数位不可超过5位" sqref="J1 K1 L1">
+      <formula1>-999.99999</formula1>
+      <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M1 M2:M65536">
-      <formula1>"01 有规律开放,02 无规律开放"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1"/>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值整数位不可超过4位，且需大于0" sqref="O1">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值整数位不可超过4位，且需大于0" sqref="P1">
       <formula1>1</formula1>
       <formula2>9999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1 R1 I2:I65536 R2:R65536">
-      <formula1>"01 是,02 否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1 N2:N65536">
-      <formula1>"01 每天开放,02 每周开放一次,03 每两周开放一次,04 每月开放一次,05 每季度开放一次,06 每半年开放一次,07 每年开放一次,99 其他规律开放周期"</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值整数位不可超过3位，小数位不可超过2位，且大于0不超过366" sqref="S1">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值整数位不可超过3位，小数位不可超过2位，且大于0不超过366" sqref="T1">
       <formula1>0</formula1>
       <formula2>366</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T1 T2:T65536">
-      <formula1>"01 申赎皆可,02 仅可申购无限制,03 仅可赎回无限制,04 仅可申购有限制,05 仅可赎回有限制,99 其他"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576 S$1:S$1048576">
+      <formula1>"01 是,02 否"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值需大于0，且必须为n(4)格式" sqref="O2:O65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
+      <formula1>"11 优先层级一,12 优先层级二,13 优先层级三,14 优先层级四,15 优先层级五,21 进取层级一,22 进取层级二,23 进取层级三,24 进取层级四,25 进取层级五"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值必须为n(8,5)格式" sqref="J2:J65536 L2:L65536">
+      <formula1>-999.99999</formula1>
+      <formula2>999.99999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值需大于等于0，且必须为n(8,5)格式" sqref="K2:K65536">
+      <formula1>0</formula1>
+      <formula2>999.99999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N$1:N$1048576">
+      <formula1>"01 有规律开放,02 无规律开放"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O$1:O$1048576">
+      <formula1>"01 每天开放,02 每周开放一次,03 每两周开放一次,04 每月开放一次,05 每季度开放一次,06 每半年开放一次,07 每年开放一次,99 其他规律开放周期"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值需大于0，且必须为n(4)格式" sqref="P2:P65536">
       <formula1>1</formula1>
       <formula2>9999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值需大于0且不超过366，必须为n(5,2)格式" sqref="S2:S65536">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值需大于0且不超过366，必须为n(5,2)格式" sqref="T2:T65536">
       <formula1>0.01</formula1>
       <formula2>366</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值必须为n(8,5)格式" sqref="J2:K65536">
-      <formula1>-999.99999</formula1>
-      <formula2>999.99999</formula2>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U$1:U$1048576">
+      <formula1>"01 申赎皆可,02 仅可申购无限制,03 仅可赎回无限制,04 仅可申购有限制,05 仅可赎回有限制,99 其他"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
   <headerFooter/>
 </worksheet>
@@ -2720,28 +2306,28 @@
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="84.875" style="6" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="84.875" style="9" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" ht="35.1" customHeight="1" spans="1:1">
+      <c r="A2" s="12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" ht="35.1" customHeight="1" spans="1:1">
-      <c r="A2" s="9" t="s">
+    <row r="3" ht="20.1" customHeight="1" spans="1:1">
+      <c r="A3" s="12" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="3" ht="20.1" customHeight="1" spans="1:1">
-      <c r="A3" s="9" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection password="EC2B" sheet="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600"/>
   <headerFooter/>
 </worksheet>
@@ -2750,63 +2336,107 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="1"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
     <col min="2" max="2" width="66.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:2">
+      <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="4">
+        <v>42724</v>
+      </c>
+    </row>
+    <row r="3" ht="81" spans="1:2">
+      <c r="A3" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="2">
-        <v>43546</v>
-      </c>
-    </row>
-    <row r="3" ht="67.5" spans="1:2">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="5" s="1" customFormat="1" spans="1:2">
+      <c r="A5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="4">
+        <v>42384</v>
+      </c>
+    </row>
+    <row r="6" ht="135" spans="1:2">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
+    <row r="7" spans="2:2">
+      <c r="B7" s="5"/>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="4">
+        <v>42244</v>
+      </c>
+    </row>
+    <row r="10" ht="94.5" spans="1:2">
+      <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="2">
-        <v>43567</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>32</v>
+      <c r="B10" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" ht="67.5" spans="1:2">
+      <c r="A13" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <sheetProtection password="EC2B" sheet="1"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>